--- a/신고신저가_20261030.xlsx
+++ b/신고신저가_20261030.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$K$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$P$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$P$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$P$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'대만'!$A$1:$P$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'홍콩'!$A$1:$P$33</definedName>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E2" t="n">
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -655,7 +655,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 美(10/29): 대형 기술주가 지수를 눌렀지만 금융과 헬스케어로 강세가 이어졌다. 나스닥은 1.38% 하락했고 알파벳 A주는 실적 발표 뒤 12.64% 떨어졌다. 반면 금융과 의료기술 업종은 각각 신고가가 신저가보다 열다섯 종목 많았다. 안과 치료제·의료기기 업체 글라우코스는 연간 매출전망 상향 발표 뒤 급등했다.</t>
+          <t>■ 美(10/29): 대형 기술주가 지수를 눌렀지만 금융과 헬스케어로 강세가 이어졌다. 나스닥은 1.38% 하락했고 알파벳 A주는 실적 발표 뒤 12.64% 떨어졌다. 반면 금융과 의료기술 업종에서는 신고가가 신저가보다 많았다. ADR을 포함하면 헤일리온의 연간 성장전망 하향에 따른 급락과 브라질 은행주 약세도 함께 보인다. 안과 치료제·의료기기 업체 글라우코스는 연간 매출전망 상향 발표 뒤 급등했다.</t>
         </is>
       </c>
     </row>
@@ -704,14 +704,24 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ 참고: 2026-10-30 08:11 KST 수집을 시작했으며 전 시장은 10월 29일 마감분이다. 미국은 이날 새벽 마감한 세션이다. 대만 TWSE 60개·TPEX 5개를 정상 수집했고 USD/TWD는 32.511이었다. 한국·일본·대만 지수 지연값을 최신 일별 자료로 보완했고, 대만 ETF는 공식 종가와 대조해 휴장일 0거래량 봉을 제외했다. 주요 종목 44개의 이유를 조사했으며 일부 촉매는 미확인이다. 공식 SEC 공시는 웹 도구로 전문을 확인했으나 직접 파일 보존 요청은 HTTP 403이었다. 일본 마감 기사는 전문을 보존했고, 나머지 검색본문만 확보한 근거와 원문 접근 한계는 조사기록에 구분했다. 장후 발표와 미국 10월 29일 정규장 움직임을 그보다 먼저 끝난 아시아 장의 원인으로 소급하지 않았다. 신규 상장 종목은 52주 이력이 부족할 수 있다.</t>
-        </is>
-      </c>
+          <t>■ 참고: 2026-10-30 08:11 KST 수집을 시작했으며 전 시장은 10월 29일 마감분이다. 미국은 이날 새벽 마감한 세션이다. 대만 TWSE 60개·TPEX 5개를 정상 수집했고 USD/TWD는 32.511이었다. 한국·일본·대만 지수 지연값을 최신 일별 자료로 보완했고, 대만 ETF는 공식 종가와 대조해 휴장일 0거래량 봉을 제외했다. 기존 44개와 추가 ADR 16개의 이유를 조사했으며 일부 촉매는 미확인이다. 공식 SEC 공시는 웹 도구로 전문을 확인했으나 직접 파일 보존 요청은 HTTP 403이었다. 일본 마감 기사는 전문을 보존했고, 나머지 검색본문만 확보한 근거와 원문 접근 한계는 조사기록에 구분했다. 장후 발표와 미국 10월 29일 정규장 움직임을 그보다 먼저 끝난 아시아 장의 원인으로 소급하지 않았다. 신규 상장 종목은 52주 이력이 부족할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>※ 3개월/52주 고저가 기준(TradingView). 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)에 도달. 전 시장10/29. TWSE60/TPEX5 정상수집. 한국·일본·대만 지수 최신값 보완 및 대만 ETF 공식종가 대조·휴장일0거래량 봉 제외. 기업별 촉매 미확인·검색본문/원문 접근 차이는 조사기록 참조.</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ 정정: 2026-10-30 오후 미국 ADR 누락을 수정했다. 미국 10월 29일 마감 기준 ADR 16종목을 추가했고, 신규 표시는 수집범위 정정으로 처음 등재됐다는 뜻도 포함한다. 미국 신고가는 75개, 신저가는 39개이며 그중 52주 신저가는 13개다. 같은 조건의 Finviz 12개를 모두 포함하고 브라데스쿠 보통주 ADR BBDO가 한 종목 더 있다. Finviz와 TradingView의 종목 커버리지 및 주식종류별 시총 차이는 미확정이며, 결과 개수를 맞추려고 BBDO를 임의 제외하지 않았다. 일본·대만·홍콩·중국A 및 ETF·지수는 오전에 검증한 10월 29일 자료를 유지했다. 미국의 과거 신고신저 기록은 ADR 미포함이므로 오늘과 전주 평균의 수집범위가 다르다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>※ 3개월/52주 고저가 기준(TradingView). 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)에 도달. 전 시장10/29. TWSE60/TPEX5 정상수집. 한국·일본·대만 지수 최신값 보완 및 대만 ETF 공식종가 대조·휴장일0거래량 봉 제외. 기업별 촉매 미확인·검색본문/원문 접근 차이는 조사기록 참조. 2026-10-30 ADR 누락 정정: 미국 stock+dr, 미국 외 시장은 원 발행 10/29 자료 유지. ADR 신규편입은 수집범위 정정이며 당일 새 가격돌파와 구분. 52주 신저13개: Finviz12개 모두포함, 추가BBDO는같은은행다른주식종류이며벤더커버리지·시총차이 미확정.</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1237,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>15</v>
@@ -1248,16 +1258,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14.3</v>
+        <v>19.3</v>
       </c>
       <c r="I2" t="n">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="J2" t="n">
-        <v>17.4</v>
+        <v>33.6</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="3">
@@ -1268,20 +1278,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -1289,16 +1299,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19.6</v>
+        <v>12.8</v>
       </c>
       <c r="I3" t="n">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="J3" t="n">
-        <v>35.1</v>
+        <v>15.8</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1313,16 +1323,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -1330,16 +1340,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J4" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -1354,16 +1364,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -1371,13 +1381,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="I5" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="K5" t="n">
         <v>6.9</v>
@@ -1395,7 +1405,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -1412,16 +1422,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>16.8</v>
+        <v>15.1</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -1453,7 +1463,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="I7" t="n">
         <v>30</v>
@@ -1477,7 +1487,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1497,10 +1507,10 @@
         <v>19.5</v>
       </c>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J8" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
         <v>6.1</v>
@@ -1518,13 +1528,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1538,13 +1548,13 @@
         <v>16.4</v>
       </c>
       <c r="I9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J9" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -1559,7 +1569,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -1576,16 +1586,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1600,7 +1610,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -1620,13 +1630,13 @@
         <v>17.7</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
@@ -1641,7 +1651,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -1658,16 +1668,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>20.4</v>
+        <v>19.6</v>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
         <v>21.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="13">
@@ -1682,7 +1692,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1699,16 +1709,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -1719,37 +1729,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>강세</t>
+        <v>-2</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="I14" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J14" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -1760,20 +1770,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -1781,16 +1791,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>15.5</v>
+        <v>22.1</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="J15" t="n">
-        <v>16.8</v>
+        <v>30.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
@@ -1801,17 +1811,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>-4</v>
@@ -1822,16 +1832,16 @@
         </is>
       </c>
       <c r="H16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>27</v>
+      </c>
+      <c r="J16" t="n">
         <v>22.1</v>
       </c>
-      <c r="I16" t="n">
-        <v>52</v>
-      </c>
-      <c r="J16" t="n">
-        <v>30.6</v>
-      </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17">
@@ -1842,20 +1852,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -1863,16 +1873,16 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="J17" t="n">
-        <v>23.2</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1883,37 +1893,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22.7</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
-        <v>30.7</v>
+        <v>14.1</v>
       </c>
       <c r="K18" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
@@ -1924,11 +1934,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1945,16 +1955,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>11.5</v>
+        <v>19.8</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J19" t="n">
-        <v>12.7</v>
+        <v>25.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="20">
@@ -1965,11 +1975,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1985,17 +1995,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>25.8</v>
+        <v>204.3</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="21">
@@ -2006,35 +2014,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D21" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>혼조</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>19.2</v>
+      </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="J21" t="n">
-        <v>204.3</v>
+        <v>22.5</v>
       </c>
       <c r="K21" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="22">
@@ -8738,7 +8748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8854,7 +8864,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GOOG US Equity</t>
+          <t>GOOGL US Equity</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -8868,19 +8878,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>282.32</v>
+        <v>283.82</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.29</v>
+        <v>-12.64</v>
       </c>
       <c r="H2" t="n">
-        <v>3468.4</v>
+        <v>3460.8</v>
       </c>
       <c r="I2" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="J2" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
@@ -8892,14 +8902,14 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" s="10" t="n">
-        <v>-26.06</v>
+        <v>-26.18</v>
       </c>
       <c r="O2" s="10" t="n">
-        <v>-30.2</v>
+        <v>-30.54</v>
       </c>
       <c r="P2" s="11" t="inlineStr">
         <is>
-          <t>알파벳 C주(검색·광고·클라우드): 매출 기대 미달과 AI 투자 현금부담 우려가 실적 발표 뒤 부각됐다.</t>
+          <t>알파벳 A주(검색·광고·클라우드): 매출 기대 미달과 AI 투자 현금부담 우려가 실적 발표 뒤 부각됐다.</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8926,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GOOGL US Equity</t>
+          <t>GOOG US Equity</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8930,19 +8940,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>283.82</v>
+        <v>282.32</v>
       </c>
       <c r="G3" t="n">
-        <v>-12.64</v>
+        <v>-12.29</v>
       </c>
       <c r="H3" t="n">
-        <v>3454.6</v>
+        <v>3460.8</v>
       </c>
       <c r="I3" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="J3" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="K3" t="n">
         <v>5.3</v>
@@ -8954,14 +8964,14 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" s="10" t="n">
-        <v>-26.18</v>
+        <v>-26.06</v>
       </c>
       <c r="O3" s="10" t="n">
-        <v>-30.54</v>
+        <v>-30.2</v>
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>알파벳 A주(검색·광고·클라우드): 매출 기대 미달과 AI 투자 현금부담 우려가 실적 발표 뒤 부각됐다.</t>
+          <t>알파벳 C주(검색·광고·클라우드): 매출 기대 미달과 AI 투자 현금부담 우려가 실적 발표 뒤 부각됐다.</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9069,7 @@
         <v>1293.1</v>
       </c>
       <c r="I5" t="n">
-        <v>30.9</v>
+        <v>30.2</v>
       </c>
       <c r="J5" t="n">
         <v>46.7</v>
@@ -9118,10 +9128,10 @@
         <v>4.16</v>
       </c>
       <c r="H6" t="n">
-        <v>556.9</v>
+        <v>557.2</v>
       </c>
       <c r="I6" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="J6" t="n">
         <v>35</v>
@@ -9235,7 +9245,7 @@
         <v>297.6</v>
       </c>
       <c r="I8" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="J8" t="n">
         <v>27.8</v>
@@ -9600,9 +9610,9 @@
       <c r="P14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -9612,36 +9622,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LIN US Equity</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>503.15</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.99</v>
+        <v>-1.41</v>
       </c>
       <c r="H15" t="n">
-        <v>231.9</v>
+        <v>243.7</v>
       </c>
       <c r="I15" t="n">
-        <v>26.3</v>
+        <v>12.9</v>
       </c>
       <c r="J15" t="n">
-        <v>32.5</v>
+        <v>23.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -9649,9 +9659,17 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="N15" s="10" t="n">
+        <v>-24.92</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>-45.04</v>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>알리바바(전자상거래·클라우드): 당일 고유 촉매는 미확인이다. 중국 기술주 약세와의 연관은 추정이다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -9659,54 +9677,50 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TD US Equity</t>
+          <t>LIN US Equity</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Toronto Dominion Bank (The)</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>127.22</v>
+        <v>503.15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>-0.99</v>
       </c>
       <c r="H16" t="n">
-        <v>214.9</v>
+        <v>231.9</v>
       </c>
       <c r="I16" t="n">
-        <v>16.2</v>
+        <v>26.2</v>
       </c>
       <c r="J16" t="n">
-        <v>19.1</v>
+        <v>32.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" s="10" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
@@ -9724,50 +9738,50 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADI US Equity</t>
+          <t>TD US Equity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Toronto Dominion Bank (The)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>433.28</v>
+        <v>127.22</v>
       </c>
       <c r="G17" t="n">
-        <v>1.17</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>210</v>
+        <v>214.9</v>
       </c>
       <c r="I17" t="n">
-        <v>26.7</v>
+        <v>16.2</v>
       </c>
       <c r="J17" t="n">
-        <v>51.4</v>
+        <v>19.1</v>
       </c>
       <c r="K17" t="n">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" s="10" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>(전일) Analog Devices(산업·자동차용 아날로그 반도체): 산업·차량용 반도체 회복 기대 속 강세 지속으로 추정. 직전 주 Texas Instruments가 관련 시장의 동반 성장을 발표했으나, 당일 개별 신규 촉매는 미확인.</t>
-        </is>
-      </c>
+      <c r="P17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9775,57 +9789,57 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TTE US Equity</t>
+          <t>ADI US Equity</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94.03</v>
+        <v>433.28</v>
       </c>
       <c r="G18" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="H18" t="n">
-        <v>209.9</v>
+        <v>210</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>26.7</v>
       </c>
       <c r="J18" t="n">
-        <v>11.9</v>
+        <v>51.4</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" s="10" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>(전일) Analog Devices(산업·자동차용 아날로그 반도체): 산업·차량용 반도체 회복 기대 속 강세 지속으로 추정. 직전 주 Texas Instruments가 관련 시장의 동반 성장을 발표했으나, 당일 개별 신규 촉매는 미확인.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9833,41 +9847,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GILD US Equity</t>
+          <t>TTE US Equity</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>165.61</v>
+        <v>94.03</v>
       </c>
       <c r="G19" t="n">
-        <v>4.03</v>
+        <v>1.24</v>
       </c>
       <c r="H19" t="n">
-        <v>205.3</v>
+        <v>209.9</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>7.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>11.9</v>
+      </c>
       <c r="K19" t="n">
-        <v>17.4</v>
+        <v>1.6</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -9889,275 +9905,299 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LMT US Equity</t>
+          <t>GILD US Equity</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>643.59</v>
+        <v>165.61</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>4.03</v>
       </c>
       <c r="H20" t="n">
-        <v>148.7</v>
+        <v>205.3</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22.9</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>14.7</v>
+        <v>17.4</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" s="10" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LMT US Equity</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lockheed Martin Corporation</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Electronic Technology</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>643.59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RIO US Equity</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rio Tinto Plc</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Non-Energy Minerals</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="n">
+        <v>-22.08</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>-26.05</v>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>리오틴토(철광석·광산): 철광석 가격 약세 우려가 반영됐다는 현지 해석이 있으나 직접 인과는 미확인이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BBVA US Equity</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Banco Bilbao Vizcaya Argentaria S.A.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="n">
+        <v>-17.51</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>-17.51</v>
+      </c>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>BBVA(스페인·중남미 은행): 실적 발표 뒤 스페인 사업과 자본비율의 기대 미달 우려가 현지에서 보도됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>OLD</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>UBER US Equity</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F24" t="n">
         <v>65.73999999999999</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G24" t="n">
         <v>0.72</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H24" t="n">
         <v>134.3</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I24" t="n">
         <v>17</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J24" t="n">
         <v>14.4</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K24" t="n">
         <v>4.9</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="n">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n">
         <v>-20.18</v>
       </c>
-      <c r="O21" s="10" t="n">
+      <c r="O24" s="10" t="n">
         <v>-34.49</v>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>(전일) 우버(차량호출·배달): 연속 강세/약세 지속(신규 촉매 미확인).</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PGR US Equity</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Progressive Corporation (The)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>230.18</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="I22" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="10" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MO US Equity</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Altria Group, Inc.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Consumer Non-Durables</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="H23" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MDT US Equity</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Medtronic plc.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Health Technology</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>97.11</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H24" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr"/>
-      <c r="O24" s="10" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -10172,12 +10212,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BNS US Equity</t>
+          <t>PGR US Equity</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bank Nova Scotia Halifax Pfd 3</t>
+          <t>Progressive Corporation (The)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10186,41 +10226,33 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>95.41</v>
+        <v>230.18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.92</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>117.5</v>
+        <v>133.8</v>
       </c>
       <c r="I25" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.1</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" s="10" t="inlineStr"/>
       <c r="P25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10230,36 +10262,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOW US Equity</t>
+          <t>BTI US Equity</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>British American Tobacco Industries, p.l.c.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>109.67</v>
+        <v>61.07</v>
       </c>
       <c r="G26" t="n">
-        <v>-26.95</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>24.1</v>
-      </c>
+        <v>129.8</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>79</v>
+        <v>15.6</v>
       </c>
       <c r="K26" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -10267,22 +10297,18 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="10" t="n">
-        <v>-31.24</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>-42.14</v>
-      </c>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" s="10" t="inlineStr"/>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>서비스나우(기업 업무 소프트웨어): 실적 발표 뒤 다음 분기 매출·수주 성장 둔화 우려로 급락했다.</t>
+          <t>브리티시아메리칸토바코(담배·니코틴제품): 당일 신규 촉매는 미확인이다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -10292,33 +10318,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FTNT US Equity</t>
+          <t>MO US Equity</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>139.1</v>
+        <v>76.75</v>
       </c>
       <c r="G27" t="n">
-        <v>-20.09</v>
+        <v>5.15</v>
       </c>
       <c r="H27" t="n">
-        <v>102.1</v>
+        <v>128.2</v>
       </c>
       <c r="I27" t="n">
-        <v>37.2</v>
+        <v>13.1</v>
       </c>
       <c r="J27" t="n">
-        <v>45.2</v>
+        <v>16.2</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
@@ -10327,17 +10353,9 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="10" t="n">
-        <v>-29.44</v>
-      </c>
-      <c r="O27" s="10" t="n">
-        <v>-29.44</v>
-      </c>
-      <c r="P27" s="11" t="inlineStr">
-        <is>
-          <t>포티넷(네트워크 보안): 실적 발표 뒤 서비스·제품 성장 지속성 우려가 부각됐다는 현지 보도가 나왔다.</t>
-        </is>
-      </c>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10352,36 +10370,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DUK US Equity</t>
+          <t>MDT US Equity</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Duke Energy Corporation (Holding Company)</t>
+          <t>Medtronic plc.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>125.9</v>
+        <v>97.11</v>
       </c>
       <c r="G28" t="n">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="H28" t="n">
-        <v>98.2</v>
+        <v>124.2</v>
       </c>
       <c r="I28" t="n">
-        <v>18.5</v>
+        <v>16.2</v>
       </c>
       <c r="J28" t="n">
-        <v>18.9</v>
+        <v>23.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -10406,106 +10424,110 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CSX US Equity</t>
+          <t>BNS US Equity</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Bank Nova Scotia Halifax Pfd 3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>52.24</v>
+        <v>95.41</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H29" t="n">
-        <v>96.3</v>
+        <v>117.5</v>
       </c>
       <c r="I29" t="n">
-        <v>22.9</v>
+        <v>14.3</v>
       </c>
       <c r="J29" t="n">
-        <v>27.1</v>
+        <v>17.5</v>
       </c>
       <c r="K29" t="n">
-        <v>6.7</v>
+        <v>2.1</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr"/>
       <c r="P29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EMR US Equity</t>
+          <t>NOW US Equity</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Emerson Electric Company</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>170.74</v>
+        <v>109.67</v>
       </c>
       <c r="G30" t="n">
-        <v>1.81</v>
+        <v>-26.95</v>
       </c>
       <c r="H30" t="n">
-        <v>95.2</v>
+        <v>113.8</v>
       </c>
       <c r="I30" t="n">
         <v>24.1</v>
       </c>
       <c r="J30" t="n">
-        <v>37.3</v>
+        <v>79</v>
       </c>
       <c r="K30" t="n">
-        <v>4.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr"/>
-      <c r="O30" s="10" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="n">
+        <v>-31.24</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>-42.14</v>
+      </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>(전일) Emerson Electric(공장 자동화·산업용 소프트웨어): 11월 4일 실적 발표를 앞두고 상승했으나, 당일 개별 신규 촉매는 미확인. 실적 기대와 수급 영향은 추정 수준.</t>
+          <t>서비스나우(기업 업무 소프트웨어): 실적 발표 뒤 다음 분기 매출·수주 성장 둔화 우려로 급락했다.</t>
         </is>
       </c>
     </row>
@@ -10522,37 +10544,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TT US Equity</t>
+          <t>FTNT US Equity</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Trane Technologies plc</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>431.1</v>
+        <v>139.1</v>
       </c>
       <c r="G31" t="n">
-        <v>-3.87</v>
+        <v>-20.09</v>
       </c>
       <c r="H31" t="n">
-        <v>94.90000000000001</v>
+        <v>102.1</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>37.2</v>
       </c>
       <c r="J31" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="K31" t="n">
-        <v>11</v>
-      </c>
+        <v>45.2</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>O</t>
@@ -10560,12 +10580,16 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" s="10" t="n">
-        <v>-12.68</v>
+        <v>-29.44</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>-14.78</v>
-      </c>
-      <c r="P31" s="11" t="inlineStr"/>
+        <v>-29.44</v>
+      </c>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>포티넷(네트워크 보안): 실적 발표 뒤 서비스·제품 성장 지속성 우려가 부각됐다는 현지 보도가 나왔다.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10580,36 +10604,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ICE US Equity</t>
+          <t>DUK US Equity</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc.</t>
+          <t>Duke Energy Corporation (Holding Company)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>163.04</v>
+        <v>125.9</v>
       </c>
       <c r="G32" t="n">
-        <v>4.54</v>
+        <v>1.89</v>
       </c>
       <c r="H32" t="n">
-        <v>91.5</v>
+        <v>98.2</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>18.9</v>
       </c>
       <c r="K32" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -10622,9 +10646,9 @@
       <c r="P32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -10634,53 +10658,45 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>APP US Equity</t>
+          <t>CSX US Equity</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Applovin Corporation</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>254.91</v>
+        <v>52.24</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.95</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>85.3</v>
+        <v>96.3</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>22.9</v>
       </c>
       <c r="J33" t="n">
-        <v>19.6</v>
+        <v>27.1</v>
       </c>
       <c r="K33" t="n">
-        <v>27</v>
+        <v>6.7</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="n">
-        <v>-41.77</v>
-      </c>
-      <c r="O33" s="10" t="n">
-        <v>-65.45999999999999</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
@@ -10689,113 +10705,119 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ECL US Equity</t>
+          <t>EMR US Equity</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Emerson Electric Company</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>300.86</v>
+        <v>170.74</v>
       </c>
       <c r="G34" t="n">
-        <v>2.89</v>
+        <v>1.81</v>
       </c>
       <c r="H34" t="n">
-        <v>84.3</v>
+        <v>95.2</v>
       </c>
       <c r="I34" t="n">
-        <v>33.6</v>
+        <v>24.1</v>
       </c>
       <c r="J34" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
+        <v>37.3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.7</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" s="11" t="inlineStr"/>
+      <c r="P34" s="11" t="inlineStr">
+        <is>
+          <t>(전일) Emerson Electric(공장 자동화·산업용 소프트웨어): 11월 4일 실적 발표를 앞두고 상승했으나, 당일 개별 신규 촉매는 미확인. 실적 기대와 수급 영향은 추정 수준.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>URI US Equity</t>
+          <t>TT US Equity</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>United Rentals, Inc.</t>
+          <t>Trane Technologies plc</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1198.68</v>
+        <v>431.1</v>
       </c>
       <c r="G35" t="n">
-        <v>2.05</v>
+        <v>-3.87</v>
       </c>
       <c r="H35" t="n">
-        <v>74.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>20.3</v>
+        <v>25.1</v>
       </c>
       <c r="J35" t="n">
-        <v>26.3</v>
+        <v>32.7</v>
       </c>
       <c r="K35" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="inlineStr"/>
-      <c r="O35" s="10" t="inlineStr"/>
-      <c r="P35" s="11" t="inlineStr">
-        <is>
-          <t>(전일) United Rentals(건설·산업장비 임대): 10월 21일 사상 최대 분기 실적과 연간 전망 상향 이후 강세가 이어진 것으로 추정. 당일 추가 신규 촉매는 미확인.</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="n">
+        <v>-12.68</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>-14.78</v>
+      </c>
+      <c r="P35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -10810,36 +10832,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NXPI US Equity</t>
+          <t>ICE US Equity</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>Intercontinental Exchange Inc.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>266</v>
+        <v>163.04</v>
       </c>
       <c r="G36" t="n">
-        <v>5.69</v>
+        <v>4.54</v>
       </c>
       <c r="H36" t="n">
-        <v>67</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>15.1</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="K36" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -10852,48 +10874,48 @@
       <c r="P36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TRGP US Equity</t>
+          <t>APP US Equity</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Targa Resources, Inc.</t>
+          <t>Applovin Corporation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>312.37</v>
+        <v>254.91</v>
       </c>
       <c r="G37" t="n">
-        <v>2.12</v>
+        <v>-1.95</v>
       </c>
       <c r="H37" t="n">
-        <v>67</v>
+        <v>85.3</v>
       </c>
       <c r="I37" t="n">
-        <v>27.3</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
-        <v>29.8</v>
+        <v>19.6</v>
       </c>
       <c r="K37" t="n">
-        <v>18.3</v>
+        <v>27</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -10905,8 +10927,12 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="10" t="inlineStr"/>
-      <c r="O37" s="10" t="inlineStr"/>
+      <c r="N37" s="10" t="n">
+        <v>-41.77</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>-65.45999999999999</v>
+      </c>
       <c r="P37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
@@ -10922,52 +10948,48 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LNG US Equity</t>
+          <t>NGG US Equity</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cheniere Energy, Inc.</t>
+          <t>National Grid Transco, PLC National Grid PLC (NEW)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>318.94</v>
+        <v>84.2</v>
       </c>
       <c r="G38" t="n">
-        <v>7.11</v>
+        <v>2.41</v>
       </c>
       <c r="H38" t="n">
-        <v>65.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>17.1</v>
+        <v>14.6</v>
       </c>
       <c r="J38" t="n">
-        <v>23.7</v>
+        <v>19.3</v>
       </c>
       <c r="K38" t="n">
-        <v>10.7</v>
+        <v>1.6</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" s="10" t="inlineStr"/>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>셰니어에너지(LNG 수출): 연간 조정 EBITDA·배분가능현금 전망 상향과 증배를 발표했다.</t>
+          <t>내셔널그리드(전력·가스망): 당일 신규 촉매는 미확인이다.</t>
         </is>
       </c>
     </row>
@@ -10977,118 +10999,120 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NDAQ US Equity</t>
+          <t>ECL US Equity</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Ecolab Inc.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>105.6</v>
+        <v>300.86</v>
       </c>
       <c r="G39" t="n">
-        <v>0.05</v>
+        <v>2.89</v>
       </c>
       <c r="H39" t="n">
-        <v>58.6</v>
+        <v>84.3</v>
       </c>
       <c r="I39" t="n">
-        <v>23.2</v>
+        <v>33.6</v>
       </c>
       <c r="J39" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.9</v>
-      </c>
+        <v>40.9</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" s="10" t="inlineStr"/>
       <c r="P39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LYG US Equity</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lloyds Banking Group Plc</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="H40" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="n">
+        <v>-16.93</v>
+      </c>
+      <c r="O40" s="10" t="n">
+        <v>-17.19</v>
+      </c>
+      <c r="P40" s="11" t="inlineStr">
+        <is>
+          <t>로이즈뱅킹(영국 은행): 실적 발표 뒤 전망 상향 부재와 예금경쟁에 따른 마진 압박 우려가 보도됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>EW US Equity</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Edwards Lifesciences Corporation</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Health Technology</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H40" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I40" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>56</v>
-      </c>
-      <c r="K40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" s="10" t="inlineStr"/>
-      <c r="O40" s="10" t="inlineStr"/>
-      <c r="P40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>OLD</t>
@@ -11096,48 +11120,54 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>URI US Equity</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>United Rentals, Inc.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>296.23</v>
+        <v>1198.68</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.43</v>
+        <v>2.05</v>
       </c>
       <c r="H41" t="n">
-        <v>46.3</v>
+        <v>74.2</v>
       </c>
       <c r="I41" t="n">
-        <v>27.4</v>
+        <v>20.3</v>
       </c>
       <c r="J41" t="n">
-        <v>34</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
+        <v>26.3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7.7</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" s="10" t="n">
-        <v>-34.44</v>
-      </c>
-      <c r="O41" s="10" t="n">
-        <v>-39.29</v>
-      </c>
-      <c r="P41" s="11" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr">
+        <is>
+          <t>(전일) United Rentals(건설·산업장비 임대): 10월 21일 사상 최대 분기 실적과 연간 전망 상향 이후 강세가 이어진 것으로 추정. 당일 추가 신규 촉매는 미확인.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -11152,36 +11182,36 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CARR US Equity</t>
+          <t>NTES US Equity</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Carrier Global Corporation</t>
+          <t>NetEase, Inc.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>55.54</v>
+        <v>112.1</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.3</v>
+        <v>-0.31</v>
       </c>
       <c r="H42" t="n">
-        <v>45.8</v>
+        <v>70</v>
       </c>
       <c r="I42" t="n">
-        <v>17.4</v>
+        <v>11.3</v>
       </c>
       <c r="J42" t="n">
-        <v>39.1</v>
+        <v>15.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -11190,12 +11220,16 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" s="10" t="n">
-        <v>-16.02</v>
+        <v>-16.14</v>
       </c>
       <c r="O42" s="10" t="n">
-        <v>-27.64</v>
-      </c>
-      <c r="P42" s="11" t="inlineStr"/>
+        <v>-24.82</v>
+      </c>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>넷이즈(온라인게임): 당일 고유 촉매는 미확인이다. 중국 기술주 약세와의 연관은 추정이다.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -11203,19 +11237,19 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ED US Equity</t>
+          <t>TRGP US Equity</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Consolidated Edison, Inc.</t>
+          <t>Targa Resources, Inc.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11224,22 +11258,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>115.49</v>
+        <v>312.37</v>
       </c>
       <c r="G43" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="H43" t="n">
-        <v>42.6</v>
+        <v>67</v>
       </c>
       <c r="I43" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>29.8</v>
       </c>
       <c r="K43" t="n">
-        <v>1.5</v>
+        <v>18.3</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -11261,43 +11295,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EL US Equity</t>
+          <t>NXPI US Equity</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Estee Lauder Companies, Inc. (The)</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>108.81</v>
+        <v>266</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.46</v>
+        <v>5.69</v>
       </c>
       <c r="H44" t="n">
-        <v>39.4</v>
+        <v>67</v>
       </c>
       <c r="I44" t="n">
-        <v>32.9</v>
+        <v>15.1</v>
       </c>
       <c r="J44" t="n">
-        <v>218.7</v>
+        <v>22.7</v>
       </c>
       <c r="K44" t="n">
-        <v>10.3</v>
+        <v>5.9</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -11322,36 +11356,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RPRX US Equity</t>
+          <t>LNG US Equity</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Royalty Pharma plc</t>
+          <t>Cheniere Energy, Inc.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>65.93000000000001</v>
+        <v>318.94</v>
       </c>
       <c r="G45" t="n">
-        <v>1.71</v>
+        <v>7.11</v>
       </c>
       <c r="H45" t="n">
-        <v>38</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="J45" t="n">
-        <v>35.1</v>
+        <v>23.7</v>
       </c>
       <c r="K45" t="n">
-        <v>4.3</v>
+        <v>10.7</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -11365,7 +11399,11 @@
       </c>
       <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>셰니어에너지(LNG 수출): 연간 조정 EBITDA·배분가능현금 전망 상향과 증배를 발표했다.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -11373,95 +11411,101 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WEC US Equity</t>
+          <t>NDAQ US Equity</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>WEC Energy Group, Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>114.63</v>
+        <v>105.6</v>
       </c>
       <c r="G46" t="n">
-        <v>3.74</v>
+        <v>0.05</v>
       </c>
       <c r="H46" t="n">
-        <v>37.4</v>
+        <v>58.6</v>
       </c>
       <c r="I46" t="n">
-        <v>21.1</v>
+        <v>23.2</v>
       </c>
       <c r="J46" t="n">
-        <v>22.2</v>
+        <v>28.9</v>
       </c>
       <c r="K46" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" s="10" t="inlineStr"/>
       <c r="P46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TTWO US Equity</t>
+          <t>EW US Equity</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>Edwards Lifesciences Corporation</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>193.39</v>
+        <v>94.44</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.97</v>
+        <v>2.9</v>
       </c>
       <c r="H47" t="n">
-        <v>36.2</v>
+        <v>54.4</v>
       </c>
       <c r="I47" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>30.1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>56</v>
+      </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -11469,12 +11513,8 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="10" t="n">
-        <v>-24.64</v>
-      </c>
-      <c r="O47" s="10" t="n">
-        <v>-27.28</v>
-      </c>
+      <c r="N47" s="10" t="inlineStr"/>
+      <c r="O47" s="10" t="inlineStr"/>
       <c r="P47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
@@ -11483,40 +11523,40 @@
           <t>신저가</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ODFL US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>172.35</v>
+        <v>296.23</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-5.43</v>
       </c>
       <c r="H48" t="n">
-        <v>35.7</v>
+        <v>46.3</v>
       </c>
       <c r="I48" t="n">
-        <v>26.1</v>
+        <v>27.4</v>
       </c>
       <c r="J48" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
@@ -11526,17 +11566,17 @@
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" s="10" t="n">
-        <v>-21.66</v>
+        <v>-34.44</v>
       </c>
       <c r="O48" s="10" t="n">
-        <v>-31.62</v>
+        <v>-39.29</v>
       </c>
       <c r="P48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -11546,36 +11586,36 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ACGL US Equity</t>
+          <t>CARR US Equity</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Arch Capital Group Ltd.</t>
+          <t>Carrier Global Corporation</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>103.94</v>
+        <v>55.54</v>
       </c>
       <c r="G49" t="n">
-        <v>1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="H49" t="n">
-        <v>35.5</v>
+        <v>45.8</v>
       </c>
       <c r="I49" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
       <c r="J49" t="n">
-        <v>8.5</v>
+        <v>39.1</v>
       </c>
       <c r="K49" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -11583,53 +11623,57 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="10" t="inlineStr"/>
-      <c r="O49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="n">
+        <v>-16.02</v>
+      </c>
+      <c r="O49" s="10" t="n">
+        <v>-27.64</v>
+      </c>
       <c r="P49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MTD US Equity</t>
+          <t>VALE US Equity</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International, Inc.</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1718.61</v>
+        <v>11.18</v>
       </c>
       <c r="G50" t="n">
-        <v>1.19</v>
+        <v>-2.53</v>
       </c>
       <c r="H50" t="n">
-        <v>34.4</v>
+        <v>44.3</v>
       </c>
       <c r="I50" t="n">
-        <v>34.8</v>
+        <v>7.2</v>
       </c>
       <c r="J50" t="n">
-        <v>38.7</v>
+        <v>23.6</v>
       </c>
       <c r="K50" t="n">
-        <v>2685.4</v>
+        <v>1.3</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -11641,9 +11685,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="10" t="inlineStr"/>
-      <c r="O50" s="10" t="inlineStr"/>
-      <c r="P50" s="11" t="inlineStr"/>
+      <c r="N50" s="10" t="n">
+        <v>-30.19</v>
+      </c>
+      <c r="O50" s="10" t="n">
+        <v>-37.68</v>
+      </c>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>발레(철광석·비철금속): 정규장 신규 촉매는 미확인이다. 당일 장후 실적을 하락 원인으로 소급하지 않는다.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -11658,12 +11710,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FTS US Equity</t>
+          <t>ED US Equity</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fortis Inc.</t>
+          <t>Consolidated Edison, Inc.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -11672,37 +11724,41 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>58.09</v>
+        <v>115.49</v>
       </c>
       <c r="G51" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="H51" t="n">
-        <v>29.7</v>
+        <v>42.6</v>
       </c>
       <c r="I51" t="n">
-        <v>22.3</v>
+        <v>18.2</v>
       </c>
       <c r="J51" t="n">
-        <v>24.2</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" s="10" t="inlineStr"/>
       <c r="P51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -11712,50 +11768,54 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SN US Equity</t>
+          <t>ABEV US Equity</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SharkNinja, Inc.</t>
+          <t>Ambev S.A.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>209.12</v>
+        <v>2.67</v>
       </c>
       <c r="G52" t="n">
-        <v>5.53</v>
+        <v>-3.96</v>
       </c>
       <c r="H52" t="n">
-        <v>29.5</v>
+        <v>41.7</v>
       </c>
       <c r="I52" t="n">
-        <v>29.7</v>
+        <v>13.8</v>
       </c>
       <c r="J52" t="n">
-        <v>42.7</v>
+        <v>13.6</v>
       </c>
       <c r="K52" t="n">
-        <v>10.4</v>
+        <v>2.4</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N52" s="10" t="inlineStr"/>
-      <c r="O52" s="10" t="inlineStr"/>
-      <c r="P52" s="11" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="O52" s="10" t="n">
+        <v>-22.61</v>
+      </c>
+      <c r="P52" s="11" t="inlineStr">
+        <is>
+          <t>암베브(맥주·음료): 분기 실적 발표 뒤 하락했다. 구체적인 기대 미달 항목은 미확인이다.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -11770,47 +11830,43 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WST US Equity</t>
+          <t>EL US Equity</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services, Inc.</t>
+          <t>Estee Lauder Companies, Inc. (The)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>416.67</v>
+        <v>108.81</v>
       </c>
       <c r="G53" t="n">
-        <v>3.23</v>
+        <v>-0.46</v>
       </c>
       <c r="H53" t="n">
-        <v>29.3</v>
+        <v>39.4</v>
       </c>
       <c r="I53" t="n">
-        <v>43.4</v>
+        <v>32.9</v>
       </c>
       <c r="J53" t="n">
-        <v>53.3</v>
+        <v>218.7</v>
       </c>
       <c r="K53" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" s="10" t="inlineStr"/>
       <c r="P53" s="11" t="inlineStr"/>
@@ -11828,90 +11884,92 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CINF US Equity</t>
+          <t>RPRX US Equity</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cincinnati Financial Corporation</t>
+          <t>Royalty Pharma plc</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>181.87</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="H54" t="n">
-        <v>27.9</v>
+        <v>38</v>
       </c>
       <c r="I54" t="n">
-        <v>20.2</v>
+        <v>13.3</v>
       </c>
       <c r="J54" t="n">
-        <v>10.7</v>
+        <v>35.1</v>
       </c>
       <c r="K54" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" s="10" t="inlineStr"/>
       <c r="P54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DGX US Equity</t>
+          <t>HLN US Equity</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Quest Diagnostics Incorporated</t>
+          <t>Haleon plc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Health Services</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>252.92</v>
+        <v>8.57</v>
       </c>
       <c r="G55" t="n">
-        <v>2.97</v>
+        <v>-14.3</v>
       </c>
       <c r="H55" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="I55" t="n">
-        <v>21.8</v>
-      </c>
+        <v>37.4</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="K55" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -11923,9 +11981,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr"/>
-      <c r="O55" s="10" t="inlineStr"/>
-      <c r="P55" s="11" t="inlineStr"/>
+      <c r="N55" s="10" t="n">
+        <v>-17.56</v>
+      </c>
+      <c r="O55" s="10" t="n">
+        <v>-24.02</v>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>헤일리온(소비자 건강제품): 감기약 수요 약화와 중국 센트룸 차질로 연간 유기매출 성장전망을 낮췄다.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -11940,36 +12006,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ULTA US Equity</t>
+          <t>WEC US Equity</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ulta Beauty, Inc.</t>
+          <t>WEC Energy Group, Inc.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>648.28</v>
+        <v>114.63</v>
       </c>
       <c r="G56" t="n">
-        <v>4.69</v>
+        <v>3.74</v>
       </c>
       <c r="H56" t="n">
-        <v>27.7</v>
+        <v>37.4</v>
       </c>
       <c r="I56" t="n">
         <v>21.2</v>
       </c>
       <c r="J56" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="K56" t="n">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -11982,110 +12048,104 @@
       <c r="P56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ERIC US Equity</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Electronic Technology</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H57" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr">
+        <is>
+          <t>에릭슨(통신장비): 당일 신규 촉매는 미확인이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>KGC US Equity</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Non-Energy Minerals</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="H57" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="I57" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N57" s="10" t="n">
-        <v>-35.48</v>
-      </c>
-      <c r="O57" s="10" t="n">
-        <v>-44.77</v>
-      </c>
-      <c r="P57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UTHR US Equity</t>
+          <t>TTWO US Equity</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>United Therapeutics Corporation</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>593.54</v>
+        <v>193.39</v>
       </c>
       <c r="G58" t="n">
-        <v>1.2</v>
+        <v>-0.97</v>
       </c>
       <c r="H58" t="n">
-        <v>25.5</v>
+        <v>36.2</v>
       </c>
       <c r="I58" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>21.2</v>
-      </c>
+        <v>23.7</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -12093,8 +12153,12 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="10" t="inlineStr"/>
-      <c r="O58" s="10" t="inlineStr"/>
+      <c r="N58" s="10" t="n">
+        <v>-24.64</v>
+      </c>
+      <c r="O58" s="10" t="n">
+        <v>-27.28</v>
+      </c>
       <c r="P58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
@@ -12110,37 +12174,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RDDT US Equity</t>
+          <t>ODFL US Equity</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Reddit, Inc.</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>129.6</v>
+        <v>172.35</v>
       </c>
       <c r="G59" t="n">
-        <v>-3.79</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>24.9</v>
+        <v>35.7</v>
       </c>
       <c r="I59" t="n">
-        <v>19.4</v>
+        <v>26.1</v>
       </c>
       <c r="J59" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>7.6</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>O</t>
@@ -12148,10 +12210,10 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" s="10" t="n">
-        <v>-29.67</v>
+        <v>-21.66</v>
       </c>
       <c r="O59" s="10" t="n">
-        <v>-50.82</v>
+        <v>-31.62</v>
       </c>
       <c r="P59" s="11" t="inlineStr"/>
     </row>
@@ -12161,19 +12223,19 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AER US Equity</t>
+          <t>ACGL US Equity</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AerCap Holdings N.V.</t>
+          <t>Arch Capital Group Ltd.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -12182,33 +12244,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>159.71</v>
+        <v>103.94</v>
       </c>
       <c r="G60" t="n">
-        <v>2.72</v>
+        <v>1.4</v>
       </c>
       <c r="H60" t="n">
-        <v>24.7</v>
+        <v>35.5</v>
       </c>
       <c r="I60" t="n">
-        <v>8.6</v>
+        <v>10.7</v>
       </c>
       <c r="J60" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="K60" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" s="10" t="inlineStr"/>
       <c r="P60" s="11" t="inlineStr"/>
@@ -12219,50 +12277,54 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ENTG US Equity</t>
+          <t>MTD US Equity</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Entegris, Inc.</t>
+          <t>Mettler-Toledo International, Inc.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>160</v>
+        <v>1718.61</v>
       </c>
       <c r="G61" t="n">
-        <v>0.43</v>
+        <v>1.19</v>
       </c>
       <c r="H61" t="n">
-        <v>24.4</v>
+        <v>34.4</v>
       </c>
       <c r="I61" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="J61" t="n">
-        <v>80.09999999999999</v>
+        <v>38.7</v>
       </c>
       <c r="K61" t="n">
-        <v>5.9</v>
+        <v>2685.4</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" s="10" t="inlineStr"/>
       <c r="P61" s="11" t="inlineStr"/>
@@ -12280,34 +12342,36 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DOW US Equity</t>
+          <t>TS US Equity</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Dow Inc.</t>
+          <t>Tenaris S.A.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>33.62</v>
+        <v>61.31</v>
       </c>
       <c r="G62" t="n">
-        <v>-1.49</v>
+        <v>1.52</v>
       </c>
       <c r="H62" t="n">
-        <v>24.3</v>
+        <v>30.9</v>
       </c>
       <c r="I62" t="n">
         <v>15.9</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>16.4</v>
+      </c>
       <c r="K62" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -12317,12 +12381,16 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" s="10" t="inlineStr"/>
       <c r="O62" s="10" t="inlineStr"/>
-      <c r="P62" s="11" t="inlineStr"/>
+      <c r="P62" s="11" t="inlineStr">
+        <is>
+          <t>테나리스(에너지용 강관): 당일 신규 촉매는 미확인이다.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -12332,36 +12400,36 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ATI US Equity</t>
+          <t>FTS US Equity</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ATI Inc.</t>
+          <t>Fortis Inc.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>175</v>
+        <v>58.09</v>
       </c>
       <c r="G63" t="n">
-        <v>5.87</v>
+        <v>1.36</v>
       </c>
       <c r="H63" t="n">
-        <v>23.8</v>
+        <v>29.7</v>
       </c>
       <c r="I63" t="n">
-        <v>28.2</v>
+        <v>22.3</v>
       </c>
       <c r="J63" t="n">
-        <v>51.2</v>
+        <v>24.2</v>
       </c>
       <c r="K63" t="n">
-        <v>12.7</v>
+        <v>1.8</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -12369,18 +12437,14 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="10" t="n">
-        <v>-28.15</v>
-      </c>
-      <c r="O63" s="10" t="n">
-        <v>-28.15</v>
-      </c>
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr"/>
       <c r="P63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -12390,36 +12454,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ALNY US Equity</t>
+          <t>SN US Equity</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals, Inc.</t>
+          <t>SharkNinja, Inc.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>174</v>
+        <v>209.12</v>
       </c>
       <c r="G64" t="n">
-        <v>-25.13</v>
+        <v>5.53</v>
       </c>
       <c r="H64" t="n">
-        <v>23.3</v>
+        <v>29.5</v>
       </c>
       <c r="I64" t="n">
-        <v>20.4</v>
+        <v>29.7</v>
       </c>
       <c r="J64" t="n">
-        <v>29.4</v>
+        <v>42.7</v>
       </c>
       <c r="K64" t="n">
-        <v>17.2</v>
+        <v>10.4</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -12431,17 +12495,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N64" s="10" t="n">
-        <v>-36.05</v>
-      </c>
-      <c r="O64" s="10" t="n">
-        <v>-63.73</v>
-      </c>
-      <c r="P64" s="11" t="inlineStr">
-        <is>
-          <t>앨나일램(RNAi 치료제): 실적 발표 뒤 급락했다. TTR 매출전망 하단 예상이 보도됐으며 연간 범위는 유지됐다.</t>
-        </is>
-      </c>
+      <c r="N64" s="10" t="inlineStr"/>
+      <c r="O64" s="10" t="inlineStr"/>
+      <c r="P64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -12456,36 +12512,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RS US Equity</t>
+          <t>WST US Equity</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Reliance, Inc.</t>
+          <t>West Pharmaceutical Services, Inc.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>439.71</v>
+        <v>416.67</v>
       </c>
       <c r="G65" t="n">
-        <v>0.58</v>
+        <v>3.23</v>
       </c>
       <c r="H65" t="n">
-        <v>22.4</v>
+        <v>29.3</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>42.9</v>
       </c>
       <c r="J65" t="n">
-        <v>20.5</v>
+        <v>53.3</v>
       </c>
       <c r="K65" t="n">
-        <v>2.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -12502,46 +12558,46 @@
       <c r="P65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VTRS US Equity</t>
+          <t>BBDO US Equity</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>Banco Bradesco Sa</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>19.2</v>
+        <v>2.49</v>
       </c>
       <c r="G66" t="n">
-        <v>2.29</v>
+        <v>-2.73</v>
       </c>
       <c r="H66" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I66" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K66" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -12553,9 +12609,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="10" t="inlineStr"/>
-      <c r="O66" s="10" t="inlineStr"/>
-      <c r="P66" s="11" t="inlineStr"/>
+      <c r="N66" s="10" t="n">
+        <v>-40.14</v>
+      </c>
+      <c r="O66" s="10" t="n">
+        <v>-40.14</v>
+      </c>
+      <c r="P66" s="11" t="inlineStr">
+        <is>
+          <t>브라데스쿠 보통주 ADR(브라질 은행): 브라질 은행주 약세와 동반 하락했다. 당일 고유 촉매는 미확인이다.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -12570,170 +12634,170 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>XPO US Equity</t>
+          <t>BBD US Equity</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>XPO, Inc.</t>
+          <t>Banco Bradesco Sa</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>183.01</v>
+        <v>2.63</v>
       </c>
       <c r="G67" t="n">
-        <v>0.73</v>
+        <v>-3.66</v>
       </c>
       <c r="H67" t="n">
-        <v>21.4</v>
+        <v>28</v>
       </c>
       <c r="I67" t="n">
-        <v>28.5</v>
+        <v>4.9</v>
       </c>
       <c r="J67" t="n">
-        <v>53.8</v>
+        <v>5.5</v>
       </c>
       <c r="K67" t="n">
-        <v>10.9</v>
+        <v>0.7</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N67" s="10" t="n">
-        <v>-14.88</v>
+        <v>-42.58</v>
       </c>
       <c r="O67" s="10" t="n">
-        <v>-21.13</v>
-      </c>
-      <c r="P67" s="11" t="inlineStr"/>
+        <v>-42.58</v>
+      </c>
+      <c r="P67" s="11" t="inlineStr">
+        <is>
+          <t>브라데스쿠 우선주 ADR(브라질 은행): 브라질 은행주 약세와 동반 하락했다. 당일 고유 촉매는 미확인이다.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CINF US Equity</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cincinnati Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>181.87</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H68" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
+      <c r="O68" s="10" t="inlineStr"/>
+      <c r="P68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>OLD</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>JBHT US Equity</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>J.B. Hunt Transport Services, Inc.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>222.06</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="H68" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="I68" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="J68" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="K68" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" s="10" t="n">
-        <v>-22.88</v>
-      </c>
-      <c r="O68" s="10" t="n">
-        <v>-25.92</v>
-      </c>
-      <c r="P68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FFIV US Equity</t>
+          <t>DGX US Equity</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Health Services</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>363.46</v>
+        <v>252.92</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.57</v>
+        <v>2.97</v>
       </c>
       <c r="H69" t="n">
-        <v>20.6</v>
+        <v>27.8</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>21.8</v>
       </c>
       <c r="J69" t="n">
-        <v>29</v>
+        <v>25.2</v>
       </c>
       <c r="K69" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" s="10" t="n">
-        <v>-24.8</v>
-      </c>
-      <c r="O69" s="10" t="n">
-        <v>-24.8</v>
-      </c>
-      <c r="P69" s="11" t="inlineStr">
-        <is>
-          <t>(전일) F5(앱 전달·보안): 분기 호실적에도 향후 EPS 전망의 시장 기대 미달 우려가 보도됐다.</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr"/>
+      <c r="P69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -12748,36 +12812,36 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EVRG US Equity</t>
+          <t>ULTA US Equity</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Evergy, Inc.</t>
+          <t>Ulta Beauty, Inc.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>85.41</v>
+        <v>648.28</v>
       </c>
       <c r="G70" t="n">
-        <v>1.38</v>
+        <v>4.69</v>
       </c>
       <c r="H70" t="n">
-        <v>19.7</v>
+        <v>27.7</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>21.2</v>
       </c>
       <c r="J70" t="n">
-        <v>21.6</v>
+        <v>23.6</v>
       </c>
       <c r="K70" t="n">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -12790,9 +12854,9 @@
       <c r="P70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -12802,48 +12866,54 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>APG US Equity</t>
+          <t>KGC US Equity</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>APi Group Corporation</t>
+          <t>Kinross Gold Corporation</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>45.02</v>
+        <v>21.6</v>
       </c>
       <c r="G71" t="n">
-        <v>8.9</v>
+        <v>-6.01</v>
       </c>
       <c r="H71" t="n">
-        <v>19.6</v>
+        <v>25.6</v>
       </c>
       <c r="I71" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J71" t="inlineStr"/>
+        <v>7.9</v>
+      </c>
+      <c r="J71" t="n">
+        <v>8.4</v>
+      </c>
       <c r="K71" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" s="10" t="inlineStr"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="11" t="inlineStr">
-        <is>
-          <t>APi그룹(소방·보안설비 서비스): 유기매출 성장과 연간 매출·조정 EBITDA 전망 상향을 발표했다.</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="n">
+        <v>-35.48</v>
+      </c>
+      <c r="O71" s="10" t="n">
+        <v>-44.77</v>
+      </c>
+      <c r="P71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -12858,47 +12928,43 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PAA US Equity</t>
+          <t>UTHR US Equity</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Plains All American Pipeline, L.P.</t>
+          <t>United Therapeutics Corporation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>26.91</v>
+        <v>593.54</v>
       </c>
       <c r="G72" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="H72" t="n">
-        <v>19</v>
+        <v>25.5</v>
       </c>
       <c r="I72" t="n">
-        <v>15.7</v>
+        <v>21.3</v>
       </c>
       <c r="J72" t="n">
-        <v>7.5</v>
+        <v>21.2</v>
       </c>
       <c r="K72" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" s="10" t="inlineStr"/>
       <c r="O72" s="10" t="inlineStr"/>
       <c r="P72" s="11" t="inlineStr"/>
@@ -12909,43 +12975,43 @@
           <t>신저가</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BG US Equity</t>
+          <t>RDDT US Equity</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bunge Limited</t>
+          <t>Reddit, Inc.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>96.02</v>
+        <v>129.6</v>
       </c>
       <c r="G73" t="n">
-        <v>-4.74</v>
+        <v>-3.79</v>
       </c>
       <c r="H73" t="n">
-        <v>18.4</v>
+        <v>24.9</v>
       </c>
       <c r="I73" t="n">
-        <v>8.9</v>
+        <v>19.7</v>
       </c>
       <c r="J73" t="n">
-        <v>18.6</v>
+        <v>30.1</v>
       </c>
       <c r="K73" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -12954,10 +13020,10 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" s="10" t="n">
-        <v>-24.67</v>
+        <v>-29.67</v>
       </c>
       <c r="O73" s="10" t="n">
-        <v>-28.8</v>
+        <v>-50.82</v>
       </c>
       <c r="P73" s="11" t="inlineStr"/>
     </row>
@@ -12974,34 +13040,36 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CRL US Equity</t>
+          <t>AER US Equity</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International, Inc.</t>
+          <t>AerCap Holdings N.V.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>376.1</v>
+        <v>159.71</v>
       </c>
       <c r="G74" t="n">
-        <v>0.57</v>
+        <v>2.72</v>
       </c>
       <c r="H74" t="n">
-        <v>18</v>
+        <v>24.7</v>
       </c>
       <c r="I74" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J74" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="K74" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -13030,36 +13098,36 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>J US Equity</t>
+          <t>ENTG US Equity</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Jacobs Solutions Inc.</t>
+          <t>Entegris, Inc.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>152.76</v>
+        <v>160</v>
       </c>
       <c r="G75" t="n">
-        <v>1.23</v>
+        <v>0.43</v>
       </c>
       <c r="H75" t="n">
-        <v>17.9</v>
+        <v>24.4</v>
       </c>
       <c r="I75" t="n">
-        <v>19.1</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>53.6</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -13084,206 +13152,212 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HST US Equity</t>
+          <t>DOW US Equity</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Host Hotels &amp; Resorts, Inc.</t>
+          <t>Dow Inc.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>25.7</v>
+        <v>33.62</v>
       </c>
       <c r="G76" t="n">
-        <v>1.7</v>
+        <v>-1.49</v>
       </c>
       <c r="H76" t="n">
-        <v>17.6</v>
+        <v>24.3</v>
       </c>
       <c r="I76" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="J76" t="n">
-        <v>17.2</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" s="10" t="inlineStr"/>
       <c r="O76" s="10" t="inlineStr"/>
       <c r="P76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ATI US Equity</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ATI Inc.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Non-Energy Minerals</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>175</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H77" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="K77" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="n">
+        <v>-28.15</v>
+      </c>
+      <c r="O77" s="10" t="n">
+        <v>-28.15</v>
+      </c>
+      <c r="P77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ALNY US Equity</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Alnylam Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>174</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-25.13</v>
+      </c>
+      <c r="H78" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="n">
+        <v>-36.05</v>
+      </c>
+      <c r="O78" s="10" t="n">
+        <v>-63.73</v>
+      </c>
+      <c r="P78" s="11" t="inlineStr">
+        <is>
+          <t>앨나일램(RNAi 치료제): 실적 발표 뒤 급락했다. TTR 매출전망 하단 예상이 보도됐으며 연간 범위는 유지됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>H US Equity</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Hyatt Hotels Corporation</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Consumer Services</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>184.3</v>
-      </c>
-      <c r="G77" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="H77" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I77" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="J77" t="n">
-        <v>228.6</v>
-      </c>
-      <c r="K77" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" s="10" t="inlineStr"/>
-      <c r="O77" s="10" t="inlineStr"/>
-      <c r="P77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>OLD</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ICLR US Equity</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>ICON plc</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Commercial Services</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>215.48</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H78" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I78" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J78" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N78" s="10" t="inlineStr"/>
-      <c r="O78" s="10" t="inlineStr"/>
-      <c r="P78" s="11" t="inlineStr">
-        <is>
-          <t>(전일) 아이콘(임상시험 수탁): 수주매출비 1.56배와 자사주 매입한도 확대를 발표했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RIVN US Equity</t>
+          <t>RS US Equity</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Rivian Automotive, Inc.</t>
+          <t>Reliance, Inc.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>11.45</v>
+        <v>439.71</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.89</v>
+        <v>0.58</v>
       </c>
       <c r="H79" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+        <v>22.4</v>
+      </c>
+      <c r="I79" t="n">
+        <v>16</v>
+      </c>
+      <c r="J79" t="n">
+        <v>20.5</v>
+      </c>
       <c r="K79" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -13295,12 +13369,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="10" t="n">
-        <v>-33.26</v>
-      </c>
-      <c r="O79" s="10" t="n">
-        <v>-49.54</v>
-      </c>
+      <c r="N79" s="10" t="inlineStr"/>
+      <c r="O79" s="10" t="inlineStr"/>
       <c r="P79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
@@ -13309,40 +13379,42 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>W US Equity</t>
+          <t>VTRS US Equity</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wayfair Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>120.12</v>
+        <v>19.2</v>
       </c>
       <c r="G80" t="n">
-        <v>5.35</v>
+        <v>2.29</v>
       </c>
       <c r="H80" t="n">
-        <v>16.5</v>
+        <v>22.1</v>
       </c>
       <c r="I80" t="n">
-        <v>34.8</v>
+        <v>7.5</v>
       </c>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>1.6</v>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>O</t>
@@ -13358,182 +13430,182 @@
       <c r="P80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>XPO US Equity</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>XPO, Inc.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>183.01</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H81" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I81" t="n">
+        <v>28</v>
+      </c>
+      <c r="J81" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" s="10" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="O81" s="10" t="n">
+        <v>-21.13</v>
+      </c>
+      <c r="P81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>OLD</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>EXEL US Equity</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Exelixis, Inc.</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Health Technology</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="G81" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="H81" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="I81" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J81" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K81" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N81" s="10" t="inlineStr"/>
-      <c r="O81" s="10" t="inlineStr"/>
-      <c r="P81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>JBHT US Equity</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>J.B. Hunt Transport Services, Inc.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>222.06</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="H82" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I82" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J82" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" s="10" t="n">
+        <v>-22.88</v>
+      </c>
+      <c r="O82" s="10" t="n">
+        <v>-25.92</v>
+      </c>
+      <c r="P82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>OLD</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ALLE US Equity</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Allegion plc</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>187.06</v>
-      </c>
-      <c r="G82" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="H82" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="I82" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="J82" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="K82" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N82" s="10" t="inlineStr"/>
-      <c r="O82" s="10" t="inlineStr"/>
-      <c r="P82" s="11" t="inlineStr">
-        <is>
-          <t>알레지온(출입문 잠금·보안장비): 연속 강세가 이어졌다. 당일 신규 촉매는 미확인이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CRBG US Equity</t>
+          <t>FFIV US Equity</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Corebridge Financial Inc.</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>35.29</v>
+        <v>363.46</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.08</v>
+        <v>-0.57</v>
       </c>
       <c r="H83" t="n">
-        <v>15.7</v>
+        <v>20.6</v>
       </c>
       <c r="I83" t="n">
-        <v>6.9</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>20.1</v>
+        <v>29</v>
       </c>
       <c r="K83" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N83" s="10" t="inlineStr"/>
-      <c r="O83" s="10" t="inlineStr"/>
-      <c r="P83" s="11" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" s="10" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="O83" s="10" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="P83" s="11" t="inlineStr">
+        <is>
+          <t>(전일) F5(앱 전달·보안): 분기 호실적에도 향후 EPS 전망의 시장 기대 미달 우려가 보도됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -13548,47 +13620,43 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EG US Equity</t>
+          <t>EVRG US Equity</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Everest Group, Ltd.</t>
+          <t>Evergy, Inc.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>400.59</v>
+        <v>85.41</v>
       </c>
       <c r="G84" t="n">
-        <v>3.54</v>
+        <v>1.38</v>
       </c>
       <c r="H84" t="n">
-        <v>15.4</v>
+        <v>19.7</v>
       </c>
       <c r="I84" t="n">
-        <v>6.9</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>8.5</v>
+        <v>21.6</v>
       </c>
       <c r="K84" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" s="10" t="inlineStr"/>
       <c r="O84" s="10" t="inlineStr"/>
       <c r="P84" s="11" t="inlineStr"/>
@@ -13599,41 +13667,41 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TRMB US Equity</t>
+          <t>APG US Equity</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>APi Group Corporation</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>65.34</v>
+        <v>45.02</v>
       </c>
       <c r="G85" t="n">
-        <v>1.54</v>
+        <v>8.9</v>
       </c>
       <c r="H85" t="n">
-        <v>15.2</v>
+        <v>19.6</v>
       </c>
       <c r="I85" t="n">
-        <v>17.1</v>
+        <v>23.1</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -13643,7 +13711,11 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" s="10" t="inlineStr"/>
       <c r="O85" s="10" t="inlineStr"/>
-      <c r="P85" s="11" t="inlineStr"/>
+      <c r="P85" s="11" t="inlineStr">
+        <is>
+          <t>APi그룹(소방·보안설비 서비스): 유기매출 성장과 연간 매출·조정 EBITDA 전망 상향을 발표했다.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -13651,43 +13723,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HALO US Equity</t>
+          <t>PAA US Equity</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Halozyme Therapeutics, Inc.</t>
+          <t>Plains All American Pipeline, L.P.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>131.18</v>
+        <v>26.91</v>
       </c>
       <c r="G86" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="H86" t="n">
-        <v>14.9</v>
+        <v>19</v>
       </c>
       <c r="I86" t="n">
-        <v>13.6</v>
+        <v>15.7</v>
       </c>
       <c r="J86" t="n">
-        <v>39.2</v>
+        <v>7.5</v>
       </c>
       <c r="K86" t="n">
-        <v>104.2</v>
+        <v>2.1</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -13704,65 +13776,69 @@
       <c r="P86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BG US Equity</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Bunge Limited</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Process Industries</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="H87" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I87" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J87" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" s="10" t="n">
+        <v>-24.67</v>
+      </c>
+      <c r="O87" s="10" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="P87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>EQH US Equity</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Equitable Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>54.61</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H87" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N87" s="10" t="inlineStr"/>
-      <c r="O87" s="10" t="inlineStr"/>
-      <c r="P87" s="11" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>OLD</t>
@@ -13770,35 +13846,35 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CHRW US Equity</t>
+          <t>CRL US Equity</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>C.H. Robinson Worldwide, Inc.</t>
+          <t>Charles River Laboratories International, Inc.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>127.43</v>
+        <v>376.1</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.13</v>
+        <v>0.57</v>
       </c>
       <c r="H88" t="n">
-        <v>14.7</v>
+        <v>18</v>
       </c>
       <c r="I88" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J88" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
+        <v>30.4</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>6.3</v>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>O</t>
@@ -13809,17 +13885,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="10" t="n">
-        <v>-19.53</v>
-      </c>
-      <c r="O88" s="10" t="n">
-        <v>-39.41</v>
-      </c>
-      <c r="P88" s="11" t="inlineStr">
-        <is>
-          <t>(전일) C.H.로빈슨(화물운송 중개): 실적 성장에도 비용 증가와 영업현금흐름 감소 부담이 보도됐다.</t>
-        </is>
-      </c>
+      <c r="N88" s="10" t="inlineStr"/>
+      <c r="O88" s="10" t="inlineStr"/>
+      <c r="P88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -13834,52 +13902,46 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GKOS US Equity</t>
+          <t>J US Equity</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Glaukos Corporation</t>
+          <t>Jacobs Solutions Inc.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>242.48</v>
+        <v>152.76</v>
       </c>
       <c r="G89" t="n">
-        <v>33.65</v>
+        <v>1.23</v>
       </c>
       <c r="H89" t="n">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I89" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="J89" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>53.6</v>
+      </c>
       <c r="K89" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" s="10" t="inlineStr"/>
       <c r="O89" s="10" t="inlineStr"/>
-      <c r="P89" s="11" t="inlineStr">
-        <is>
-          <t>글라우코스(안과 의약품·의료기기): 분기 매출 성장과 연간 매출전망 상향 발표 뒤 급등했다.</t>
-        </is>
-      </c>
+      <c r="P89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -13894,35 +13956,37 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EHC US Equity</t>
+          <t>HST US Equity</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Encompass Health Corporation</t>
+          <t>Host Hotels &amp; Resorts, Inc.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Health Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>131.49</v>
+        <v>25.7</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="H90" t="n">
-        <v>13</v>
+        <v>17.6</v>
       </c>
       <c r="I90" t="n">
-        <v>20</v>
+        <v>25.4</v>
       </c>
       <c r="J90" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2.8</v>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>O</t>
@@ -13935,77 +13999,61 @@
       </c>
       <c r="N90" s="10" t="inlineStr"/>
       <c r="O90" s="10" t="inlineStr"/>
-      <c r="P90" s="11" t="inlineStr">
-        <is>
-          <t>인컴패스헬스(입원 재활병원): 연간 매출·조정 EBITDA·조정 EPS 전망 상향 발표 뒤 상승했다.</t>
-        </is>
-      </c>
+      <c r="P90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LII US Equity</t>
+          <t>H US Equity</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lennox International, Inc.</t>
+          <t>Hyatt Hotels Corporation</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>348.12</v>
+        <v>184.3</v>
       </c>
       <c r="G91" t="n">
-        <v>4.65</v>
+        <v>6.32</v>
       </c>
       <c r="H91" t="n">
-        <v>12</v>
+        <v>17.4</v>
       </c>
       <c r="I91" t="n">
-        <v>15.2</v>
+        <v>41.9</v>
       </c>
       <c r="J91" t="n">
-        <v>16.2</v>
+        <v>228.6</v>
       </c>
       <c r="K91" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N91" s="10" t="n">
-        <v>-23.74</v>
-      </c>
-      <c r="O91" s="10" t="n">
-        <v>-40.72</v>
-      </c>
-      <c r="P91" s="11" t="inlineStr">
-        <is>
-          <t>(전일) 레녹스(냉난방장비): 연간 조정EPS 전망을 종전보다 낮췄다.</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr"/>
+      <c r="P91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -14013,57 +14061,65 @@
           <t>신저가</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WTS US Equity</t>
+          <t>BSBR US Equity</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Watts Water Technologies, Inc.</t>
+          <t>Banco Santander Brasil SA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>350.89</v>
+        <v>4.57</v>
       </c>
       <c r="G92" t="n">
-        <v>2.34</v>
+        <v>0.66</v>
       </c>
       <c r="H92" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="I92" t="n">
-        <v>26.3</v>
+        <v>6</v>
       </c>
       <c r="J92" t="n">
-        <v>30.6</v>
+        <v>13.1</v>
       </c>
       <c r="K92" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N92" s="10" t="n">
-        <v>-10.84</v>
+        <v>-24.46</v>
       </c>
       <c r="O92" s="10" t="n">
-        <v>-11.06</v>
-      </c>
-      <c r="P92" s="11" t="inlineStr"/>
+        <v>-37.57</v>
+      </c>
+      <c r="P92" s="11" t="inlineStr">
+        <is>
+          <t>산탄데르브라질(브라질 은행): 당일 신규 촉매는 미확인이다. 장중 저점 도달과 상승 마감을 구분한다.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -14078,48 +14134,48 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BWA US Equity</t>
+          <t>RIVN US Equity</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BorgWarner Inc.</t>
+          <t>Rivian Automotive, Inc.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>53.3</v>
+        <v>11.45</v>
       </c>
       <c r="G93" t="n">
-        <v>-4.7</v>
+        <v>-1.89</v>
       </c>
       <c r="H93" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I93" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J93" t="n">
-        <v>27.1</v>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N93" s="10" t="n">
-        <v>-24.91</v>
+        <v>-33.26</v>
       </c>
       <c r="O93" s="10" t="n">
-        <v>-32.38</v>
+        <v>-49.54</v>
       </c>
       <c r="P93" s="11" t="inlineStr"/>
     </row>
@@ -14136,48 +14192,52 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ENSG US Equity</t>
+          <t>ICLR US Equity</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>The Ensign Group, Inc.</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Health Services</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>186.32</v>
+        <v>215.48</v>
       </c>
       <c r="G94" t="n">
-        <v>1.2</v>
+        <v>0.62</v>
       </c>
       <c r="H94" t="n">
-        <v>10.9</v>
+        <v>16.6</v>
       </c>
       <c r="I94" t="n">
-        <v>21.8</v>
+        <v>19.1</v>
       </c>
       <c r="J94" t="n">
-        <v>27.7</v>
+        <v>37.1</v>
       </c>
       <c r="K94" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N94" s="10" t="inlineStr"/>
       <c r="O94" s="10" t="inlineStr"/>
       <c r="P94" s="11" t="inlineStr">
         <is>
-          <t>(전일) 엔사인그룹(요양시설 운영): 분기 EPS가 시장 예상을 웃돌았다는 보도가 나왔다.</t>
+          <t>(전일) 아이콘(임상시험 수탁): 수주매출비 1.56배와 자사주 매입한도 확대를 발표했다.</t>
         </is>
       </c>
     </row>
@@ -14187,50 +14247,50 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AES US Equity</t>
+          <t>W US Equity</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>The AES Corporation</t>
+          <t>Wayfair Inc.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>15.05</v>
+        <v>120.12</v>
       </c>
       <c r="G95" t="n">
-        <v>0.47</v>
+        <v>5.35</v>
       </c>
       <c r="H95" t="n">
-        <v>10.7</v>
+        <v>16.5</v>
       </c>
       <c r="I95" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J95" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K95" t="n">
-        <v>2.2</v>
-      </c>
+        <v>34.8</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N95" s="10" t="inlineStr"/>
       <c r="O95" s="10" t="inlineStr"/>
       <c r="P95" s="11" t="inlineStr"/>
@@ -14241,43 +14301,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AMG US Equity</t>
+          <t>EXEL US Equity</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Affiliated Managers Group, Inc.</t>
+          <t>Exelixis, Inc.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>399.02</v>
+        <v>66.2</v>
       </c>
       <c r="G96" t="n">
-        <v>1.47</v>
+        <v>-0.12</v>
       </c>
       <c r="H96" t="n">
-        <v>10.3</v>
+        <v>16.4</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>17.3</v>
       </c>
       <c r="J96" t="n">
-        <v>13.9</v>
+        <v>20.8</v>
       </c>
       <c r="K96" t="n">
-        <v>3.4</v>
+        <v>8.9</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -14294,62 +14354,66 @@
       <c r="P96" s="11" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SCI US Equity</t>
+          <t>ALLE US Equity</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Service Corporation International</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>75.17</v>
+        <v>187.06</v>
       </c>
       <c r="G97" t="n">
-        <v>-8.699999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="H97" t="n">
-        <v>10.2</v>
+        <v>15.8</v>
       </c>
       <c r="I97" t="n">
-        <v>16.8</v>
+        <v>18.8</v>
       </c>
       <c r="J97" t="n">
-        <v>18.6</v>
+        <v>23.3</v>
       </c>
       <c r="K97" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" s="10" t="n">
-        <v>-14.27</v>
-      </c>
-      <c r="O97" s="10" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="P97" s="11" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" s="10" t="inlineStr"/>
+      <c r="P97" s="11" t="inlineStr">
+        <is>
+          <t>알레지온(출입문 잠금·보안장비): 연속 강세가 이어졌다. 당일 신규 촉매는 미확인이다.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -14357,43 +14421,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TTC US Equity</t>
+          <t>CRBG US Equity</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Toro Company (The)</t>
+          <t>Corebridge Financial Inc.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>107.38</v>
+        <v>35.29</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51</v>
+        <v>-0.08</v>
       </c>
       <c r="H98" t="n">
-        <v>10.2</v>
+        <v>15.7</v>
       </c>
       <c r="I98" t="n">
-        <v>21.7</v>
+        <v>6.9</v>
       </c>
       <c r="J98" t="n">
-        <v>28.8</v>
+        <v>20.1</v>
       </c>
       <c r="K98" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -14422,36 +14486,36 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LTH US Equity</t>
+          <t>EG US Equity</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Life Time Group Holdings, Inc.</t>
+          <t>Everest Group, Ltd.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>45.35</v>
+        <v>400.59</v>
       </c>
       <c r="G99" t="n">
-        <v>5.12</v>
+        <v>3.54</v>
       </c>
       <c r="H99" t="n">
-        <v>10.1</v>
+        <v>15.4</v>
       </c>
       <c r="I99" t="n">
-        <v>26.2</v>
+        <v>6.9</v>
       </c>
       <c r="J99" t="n">
-        <v>24.8</v>
+        <v>8.5</v>
       </c>
       <c r="K99" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -14467,8 +14531,940 @@
       <c r="O99" s="10" t="inlineStr"/>
       <c r="P99" s="11" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TRMB US Equity</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Trimble Inc.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Technology Services</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H100" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I100" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>3</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
+      <c r="O100" s="10" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EQH US Equity</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Equitable Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H101" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I101" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N101" s="10" t="inlineStr"/>
+      <c r="O101" s="10" t="inlineStr"/>
+      <c r="P101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HALO US Equity</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Halozyme Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>131.18</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H102" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I102" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J102" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="K102" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N102" s="10" t="inlineStr"/>
+      <c r="O102" s="10" t="inlineStr"/>
+      <c r="P102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CHRW US Equity</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C.H. Robinson Worldwide, Inc.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>127.43</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="H103" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I103" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N103" s="10" t="n">
+        <v>-19.53</v>
+      </c>
+      <c r="O103" s="10" t="n">
+        <v>-39.41</v>
+      </c>
+      <c r="P103" s="11" t="inlineStr">
+        <is>
+          <t>(전일) C.H.로빈슨(화물운송 중개): 실적 성장에도 비용 증가와 영업현금흐름 감소 부담이 보도됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>GKOS US Equity</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Glaukos Corporation</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>242.48</v>
+      </c>
+      <c r="G104" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="H104" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I104" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>20</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N104" s="10" t="inlineStr"/>
+      <c r="O104" s="10" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr">
+        <is>
+          <t>글라우코스(안과 의약품·의료기기): 분기 매출 성장과 연간 매출전망 상향 발표 뒤 급등했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EHC US Equity</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Encompass Health Corporation</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Health Services</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>131.49</v>
+      </c>
+      <c r="G105" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H105" t="n">
+        <v>13</v>
+      </c>
+      <c r="I105" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J105" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N105" s="10" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr">
+        <is>
+          <t>인컴패스헬스(입원 재활병원): 연간 매출·조정 EBITDA·조정 EPS 전망 상향 발표 뒤 상승했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LII US Equity</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lennox International, Inc.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Producer Manufacturing</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H106" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I106" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>9</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N106" s="10" t="n">
+        <v>-23.74</v>
+      </c>
+      <c r="O106" s="10" t="n">
+        <v>-40.72</v>
+      </c>
+      <c r="P106" s="11" t="inlineStr">
+        <is>
+          <t>(전일) 레녹스(냉난방장비): 연간 조정EPS 전망을 종전보다 낮췄다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>WTS US Equity</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Watts Water Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Producer Manufacturing</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H107" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I107" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" s="10" t="n">
+        <v>-10.84</v>
+      </c>
+      <c r="O107" s="10" t="n">
+        <v>-11.06</v>
+      </c>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>RDY US Equity</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H108" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I108" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J108" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
+      <c r="O108" s="10" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr">
+        <is>
+          <t>닥터레디스(제네릭·의약품): 당일 신규 촉매는 미확인이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ENSG US Equity</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>The Ensign Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Health Services</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>186.32</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I109" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J109" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="K109" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
+      <c r="O109" s="10" t="inlineStr"/>
+      <c r="P109" s="11" t="inlineStr">
+        <is>
+          <t>(전일) 엔사인그룹(요양시설 운영): 분기 EPS가 시장 예상을 웃돌았다는 보도가 나왔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BWA US Equity</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BorgWarner Inc.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Producer Manufacturing</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I110" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J110" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" s="10" t="n">
+        <v>-24.91</v>
+      </c>
+      <c r="O110" s="10" t="n">
+        <v>-32.38</v>
+      </c>
+      <c r="P110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AES US Equity</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>The AES Corporation</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H111" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J111" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
+      <c r="O111" s="10" t="inlineStr"/>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMG US Equity</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Affiliated Managers Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>399.02</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H112" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I112" t="n">
+        <v>10</v>
+      </c>
+      <c r="J112" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N112" s="10" t="inlineStr"/>
+      <c r="O112" s="10" t="inlineStr"/>
+      <c r="P112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SCI US Equity</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Service Corporation International</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>75.17</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="H113" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I113" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K113" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" s="10" t="n">
+        <v>-14.27</v>
+      </c>
+      <c r="O113" s="10" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>TTC US Equity</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Toro Company (The)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Producer Manufacturing</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H114" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J114" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K114" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N114" s="10" t="inlineStr"/>
+      <c r="O114" s="10" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>LTH US Equity</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Life Time Group Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="G115" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="H115" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J115" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K115" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N115" s="10" t="inlineStr"/>
+      <c r="O115" s="10" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P99"/>
+  <autoFilter ref="A1:P115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
